--- a/astro-site/public/dl/plan-negocio-food-truck/plan-financiero-food-truck.xlsx
+++ b/astro-site/public/dl/plan-negocio-food-truck/plan-financiero-food-truck.xlsx
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
         <v>0.035903840149859506</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Vehículo food truck (nuevo o segunda mano), Adaptación y rotulación vehículo, Instalación gas (si aplica), Depósito de agua + aguas residuales y Proyecto técnico sanitario), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Vehículo food truck (nuevo o segunda mano), Adaptación y rotulación vehículo, Instalación gas (si aplica), Depósito de agua + aguas residuales y Proyecto técnico sanitario), no "&amp;"del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Vehículo food truck (nuevo o segunda mano), Adaptación y rotulación vehículo, Instalación gas (si aplica), Depósito de agua + aguas residuales y Proyecto técnico sanitario), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2188,7 +2188,7 @@
         <v>12672.24</v>
       </c>
       <c r="D28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
         <v>6648.0</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencias y permisos (promedio), Stock inicial de producto, Marketing lanzamiento, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencias y permisos (promedio), Stock inicial de producto, Marketing lanzamiento, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón "&amp;"operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencias y permisos (promedio), Stock inicial de producto, Marketing lanzamiento, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 25453 € de los 81997 € de inversión.</v>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-food-truck/plan-financiero-food-truck.xlsx
+++ b/astro-site/public/dl/plan-negocio-food-truck/plan-financiero-food-truck.xlsx
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-food-truck/plan-financiero-food-truck.xlsx
+++ b/astro-site/public/dl/plan-negocio-food-truck/plan-financiero-food-truck.xlsx
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
         <v>0.035903840149859506</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Vehículo food truck (nuevo o segunda mano), Adaptación y rotulación vehículo, Instalación gas (si aplica), Depósito de agua + aguas residuales y Proyecto técnico sanitario), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Vehículo food truck (nuevo o segunda mano), Adaptación y rotulación vehículo, Instalación gas (si aplica), Depósito de agua + aguas residuales y Proyecto técnico sanitario), no "&amp;"del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Vehículo food truck (nuevo o segunda mano), Adaptación y rotulación vehículo, Instalación gas (si aplica), Depósito de agua + aguas residuales y Proyecto técnico sanitario), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2188,7 +2188,7 @@
         <v>12672.24</v>
       </c>
       <c r="D28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
         <v>6648.0</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencias y permisos (promedio), Stock inicial de producto, Marketing lanzamiento, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencias y permisos (promedio), Stock inicial de producto, Marketing lanzamiento, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón "&amp;"operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría + registro, Licencias y permisos (promedio), Stock inicial de producto, Marketing lanzamiento, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 25453 € de los 81997 € de inversión.</v>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
